--- a/ig/DM-SIDOBA/CodeSystem-tre-r420-droit-prestation.xlsx
+++ b/ig/DM-SIDOBA/CodeSystem-tre-r420-droit-prestation.xlsx
@@ -250,7 +250,7 @@
     <t>AVA (Assurance vieillesse des aidants)</t>
   </si>
   <si>
-    <t>une affiliation gratuite à l'assurance vieillesse des aidants (AVA)</t>
+    <t>Une affiliation gratuite à l'assurance vieillesse des aidants (AVA)</t>
   </si>
   <si>
     <t>4</t>
@@ -259,7 +259,7 @@
     <t>Carte mobilité inclusion</t>
   </si>
   <si>
-    <t>une carte mobilité inclusion (CMI)</t>
+    <t>Une carte mobilité inclusion (CMI)</t>
   </si>
   <si>
     <t>5</t>
@@ -268,7 +268,7 @@
     <t>PCH</t>
   </si>
   <si>
-    <t>une prestation de compensation du handicap (PCH)</t>
+    <t>Une prestation de compensation du handicap (PCH)</t>
   </si>
   <si>
     <t>6</t>
@@ -277,7 +277,7 @@
     <t>AEEH et son complément</t>
   </si>
   <si>
-    <t>une allocation d'éducation de l'enfant handicapé (AEEH) et son complément</t>
+    <t>Une allocation d'éducation de l'enfant handicapé (AEEH) et son complément</t>
   </si>
   <si>
     <t>7</t>
@@ -286,7 +286,7 @@
     <t>Orientation ESMS Enfants</t>
   </si>
   <si>
-    <t>une orientation vers un établissement ou service médico-social Enfants</t>
+    <t>Une orientation vers un établissement ou service médico-social Enfants</t>
   </si>
   <si>
     <t>8</t>
@@ -295,7 +295,7 @@
     <t>Orientation scolaire</t>
   </si>
   <si>
-    <t>une orientation scolaire</t>
+    <t>Une orientation scolaire</t>
   </si>
   <si>
     <t>9</t>
@@ -316,7 +316,7 @@
     <t>Formation et insertion professionnelle</t>
   </si>
   <si>
-    <t>une formation ou une insertion professionnelle</t>
+    <t>Une formation ou une insertion professionnelle</t>
   </si>
   <si>
     <t>12</t>
@@ -331,7 +331,7 @@
     <t>Orientation ESMS Adultes</t>
   </si>
   <si>
-    <t>une orientation vers un établissement ou service médico-social Adultes</t>
+    <t>Une orientation vers un établissement ou service médico-social Adultes</t>
   </si>
   <si>
     <t>14</t>
